--- a/RUN/RUN_Producto.xlsx
+++ b/RUN/RUN_Producto.xlsx
@@ -2801,13 +2801,13 @@
         <v>0.04085295208781693</v>
       </c>
       <c r="L2" s="2">
-        <v>112.2262160580291</v>
+        <v>110.6984979308547</v>
       </c>
       <c r="M2" s="2">
-        <v>0.4584772227615653</v>
+        <v>0.4522360432162508</v>
       </c>
       <c r="N2" s="2">
-        <v>0.04584772227615654</v>
+        <v>0.04522360432162508</v>
       </c>
     </row>
     <row r="3" spans="1:14">
